--- a/products/store_b/out/01_Wedding_Budget_Tracker.xlsx
+++ b/products/store_b/out/01_Wedding_Budget_Tracker.xlsx
@@ -1009,11 +1009,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="79144134"/>
-        <c:axId val="30765848"/>
+        <c:axId val="75890141"/>
+        <c:axId val="31000280"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="79144134"/>
+        <c:axId val="75890141"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1045,7 +1045,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30765848"/>
+        <c:crossAx val="31000280"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1053,7 +1053,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30765848"/>
+        <c:axId val="31000280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1095,7 +1095,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79144134"/>
+        <c:crossAx val="75890141"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
